--- a/exports/MOTHERSON_full_report.xlsx
+++ b/exports/MOTHERSON_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>4.9</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44574.55208333334</v>
+        <v>44575.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>95.17</v>
+        <v>83.7</v>
       </c>
       <c r="I2" t="n">
         <v>92.97196375</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07000000000000001</v>
+        <v>-11.99</v>
       </c>
       <c r="L2" t="n">
-        <v>2.81</v>
+        <v>14.65</v>
       </c>
       <c r="M2" t="n">
         <v>0.03</v>
       </c>
       <c r="N2" t="n">
-        <v>3.34</v>
+        <v>13.39</v>
       </c>
       <c r="O2" t="n">
         <v>0.8100000000000001</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>22.28</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44655.38541666666</v>
+        <v>44655.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>62.83</v>
+        <v>63.7</v>
       </c>
       <c r="I3" t="n">
         <v>62.89529745877245</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>80</v>
+        <v>80.16666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>24.93</v>
+        <v>23.89</v>
       </c>
       <c r="L3" t="n">
         <v>18.88</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>6.81</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>61.87</v>
+        <v>60.9</v>
       </c>
       <c r="I4" t="n">
         <v>61.00043778821149</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>9</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.87</v>
+        <v>-4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>4.4</v>
+        <v>4.76</v>
       </c>
       <c r="M4" t="n">
         <v>0.51</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>6.75</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44698.38541666666</v>
+        <v>44698.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>55.43</v>
+        <v>56.27</v>
       </c>
       <c r="I5" t="n">
         <v>55.46082461291511</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>8.98</v>
+        <v>7.6</v>
       </c>
       <c r="L5" t="n">
         <v>3.61</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.5</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44727.55208333334</v>
+        <v>44728.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>53.43</v>
+        <v>52.53</v>
       </c>
       <c r="I6" t="n">
         <v>53.30170221391326</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.05</v>
+        <v>-6.65</v>
       </c>
       <c r="L6" t="n">
         <v>8</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>8.98</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44735.55208333334</v>
+        <v>44736.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>53.03</v>
+        <v>53.9</v>
       </c>
       <c r="I7" t="n">
         <v>53.88632310670189</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.95</v>
+        <v>-2.61</v>
       </c>
       <c r="L7" t="n">
         <v>4.32</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>7.52</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44747.38541666666</v>
+        <v>44747.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>51.93</v>
+        <v>50.83</v>
       </c>
       <c r="I8" t="n">
         <v>51.72421679354591</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.65</v>
+        <v>-5.7</v>
       </c>
       <c r="L8" t="n">
-        <v>4.58</v>
+        <v>5.94</v>
       </c>
       <c r="M8" t="n">
         <v>2.06</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>7.55</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44760.38541666666</v>
+        <v>44760.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>54.17</v>
+        <v>56.3</v>
       </c>
       <c r="I9" t="n">
         <v>54.59528410877032</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.57</v>
+        <v>-10.76</v>
       </c>
       <c r="L9" t="n">
-        <v>6.77</v>
+        <v>11.02</v>
       </c>
       <c r="M9" t="n">
         <v>0.89</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>7.26</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44781.55208333334</v>
+        <v>44783.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>57.23</v>
+        <v>54</v>
       </c>
       <c r="I10" t="n">
         <v>55.5834994930211</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>21</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>1.65</v>
+        <v>-4.09</v>
       </c>
       <c r="L10" t="n">
-        <v>3.78</v>
+        <v>4.32</v>
       </c>
       <c r="M10" t="n">
         <v>0.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.12</v>
+        <v>5.42</v>
       </c>
       <c r="O10" t="n">
         <v>6.03</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>11.87</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44790.38541666666</v>
+        <v>44790.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>58.03</v>
+        <v>58.6</v>
       </c>
       <c r="I11" t="n">
         <v>58.13763774301076</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-7.46</v>
+        <v>-8.52</v>
       </c>
       <c r="L11" t="n">
-        <v>7.83</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M11" t="n">
         <v>0.97</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>6.9</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44799.55208333334</v>
+        <v>44802.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>55.6</v>
+        <v>53.77</v>
       </c>
       <c r="I12" t="n">
         <v>54.69106419021661</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.12</v>
+        <v>-8.24</v>
       </c>
       <c r="L12" t="n">
-        <v>7.12</v>
+        <v>8.58</v>
       </c>
       <c r="M12" t="n">
-        <v>1.02</v>
+        <v>2.46</v>
       </c>
       <c r="N12" t="n">
-        <v>2.62</v>
+        <v>3.06</v>
       </c>
       <c r="O12" t="n">
         <v>2.81</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>6.66</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44817.38541666666</v>
+        <v>44817.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>56.67</v>
+        <v>56.97</v>
       </c>
       <c r="I13" t="n">
         <v>56.94616037671087</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.39</v>
+        <v>-5.95</v>
       </c>
       <c r="L13" t="n">
-        <v>5.64</v>
+        <v>7.18</v>
       </c>
       <c r="M13" t="n">
         <v>1.1</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>3.74</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44823.38541666666</v>
+        <v>44823.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>54.93</v>
+        <v>54.8</v>
       </c>
       <c r="I14" t="n">
         <v>54.8410141132404</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.58</v>
+        <v>-3.81</v>
       </c>
       <c r="L14" t="n">
         <v>4.56</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.14</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44869.55208333334</v>
+        <v>44872.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>43.37</v>
+        <v>44.53</v>
       </c>
       <c r="I15" t="n">
         <v>44.33943448466532</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>46</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K15" t="n">
-        <v>20.86</v>
+        <v>18.74</v>
       </c>
       <c r="L15" t="n">
         <v>2.24</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.54</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44910.38541666666</v>
+        <v>44910.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>47.9</v>
+        <v>47.67</v>
       </c>
       <c r="I16" t="n">
         <v>47.7686321835844</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>38</v>
+        <v>38.16666666666666</v>
       </c>
       <c r="K16" t="n">
-        <v>7.57</v>
+        <v>7.05</v>
       </c>
       <c r="L16" t="n">
         <v>1.8</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>4.54</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44918.55208333334</v>
+        <v>44921.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>44.87</v>
+        <v>47.7</v>
       </c>
       <c r="I17" t="n">
         <v>47.41989709708206</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>5.87</v>
+        <v>-0.06</v>
       </c>
       <c r="L17" t="n">
         <v>0.63</v>
@@ -1410,7 +1613,7 @@
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>1.08</v>
+        <v>6.46</v>
       </c>
       <c r="O17" t="n">
         <v>-1.16</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>10.98</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44942.55208333334</v>
+        <v>44943.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>50.47</v>
+        <v>49.7</v>
       </c>
       <c r="I18" t="n">
         <v>49.89663440485025</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K18" t="n">
-        <v>5.81</v>
+        <v>4.19</v>
       </c>
       <c r="L18" t="n">
         <v>7.27</v>
       </c>
       <c r="M18" t="n">
-        <v>1.15</v>
+        <v>2.66</v>
       </c>
       <c r="N18" t="n">
         <v>2</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>7.99</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44960.38541666666</v>
+        <v>44960.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>50.03</v>
+        <v>50.67</v>
       </c>
       <c r="I19" t="n">
         <v>50.22142180201313</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.66</v>
+        <v>-1.95</v>
       </c>
       <c r="L19" t="n">
         <v>3.56</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>7.47</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44981.55208333334</v>
+        <v>44984.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>54.9</v>
+        <v>52</v>
       </c>
       <c r="I20" t="n">
         <v>52.35792532508338</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>21</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>8.35</v>
+        <v>2.62</v>
       </c>
       <c r="L20" t="n">
         <v>1.78</v>
@@ -1581,7 +1820,7 @@
         <v>0.55</v>
       </c>
       <c r="N20" t="n">
-        <v>2.27</v>
+        <v>4.43</v>
       </c>
       <c r="O20" t="n">
         <v>1.28</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.140000000000001</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44991.38541666666</v>
+        <v>44991.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>55.4</v>
+        <v>55.6</v>
       </c>
       <c r="I21" t="n">
         <v>55.41218048668247</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>-6.54</v>
+        <v>-6.92</v>
       </c>
       <c r="L21" t="n">
         <v>7.44</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>5.51</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44998.55208333334</v>
+        <v>44999.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>53.3</v>
+        <v>52.23</v>
       </c>
       <c r="I22" t="n">
         <v>52.78626277594029</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.14</v>
+        <v>-6.06</v>
       </c>
       <c r="L22" t="n">
-        <v>4.91</v>
+        <v>6.12</v>
       </c>
       <c r="M22" t="n">
         <v>0.98</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.11</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45016.38541666666</v>
+        <v>45016.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>44.27</v>
+        <v>44.73</v>
       </c>
       <c r="I23" t="n">
         <v>44.71695569280902</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>15.24</v>
+        <v>14.36</v>
       </c>
       <c r="L23" t="n">
         <v>2.3</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>7.01</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45140.38541666666</v>
+        <v>45140.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>64.90000000000001</v>
+        <v>64.17</v>
       </c>
       <c r="I24" t="n">
         <v>64.2391660187842</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>123.8333333333333</v>
+        <v>124</v>
       </c>
       <c r="K24" t="n">
-        <v>45.09</v>
+        <v>43.46</v>
       </c>
       <c r="L24" t="n">
         <v>1.48</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>166</v>
+        <v>167</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>5.43</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45170.55208333334</v>
+        <v>45173.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>65.2</v>
+        <v>66.17</v>
       </c>
       <c r="I25" t="n">
         <v>65.83015782425204</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>30</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.61</v>
+        <v>-3.12</v>
       </c>
       <c r="L25" t="n">
         <v>6.86</v>
@@ -1866,7 +2165,7 @@
         <v>2.69</v>
       </c>
       <c r="N25" t="n">
-        <v>2.24</v>
+        <v>5.17</v>
       </c>
       <c r="O25" t="n">
         <v>-2.58</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.23</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45189.55208333334</v>
+        <v>45190.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>65.67</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I26" t="n">
         <v>64.52282082613621</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.76</v>
+        <v>-3.13</v>
       </c>
       <c r="L26" t="n">
         <v>3.58</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>6.22</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45209.55208333334</v>
+        <v>45210.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>62.47</v>
+        <v>63.53</v>
       </c>
       <c r="I27" t="n">
         <v>63.00677885271168</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>2.54</v>
+        <v>0.89</v>
       </c>
       <c r="L27" t="n">
         <v>2.54</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>5.66</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45219.38541666666</v>
+        <v>45219.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>62.53</v>
+        <v>62.27</v>
       </c>
       <c r="I28" t="n">
         <v>62.43030225955615</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.57</v>
+        <v>-1.98</v>
       </c>
       <c r="L28" t="n">
-        <v>1.89</v>
+        <v>2.57</v>
       </c>
       <c r="M28" t="n">
         <v>0.9</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>4.46</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45258.55208333334</v>
+        <v>45259.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>60.07</v>
+        <v>61.1</v>
       </c>
       <c r="I29" t="n">
         <v>60.69724322183294</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>39</v>
+        <v>39.83333333333334</v>
       </c>
       <c r="K29" t="n">
-        <v>3.53</v>
+        <v>1.88</v>
       </c>
       <c r="L29" t="n">
         <v>0.9</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>5.03</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>63.93</v>
+        <v>61.57</v>
       </c>
       <c r="I30" t="n">
         <v>62.69139909497219</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>4.63</v>
+        <v>0.77</v>
       </c>
       <c r="L30" t="n">
         <v>1.75</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>7.35</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45288.55208333334</v>
+        <v>45289.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>65.23</v>
+        <v>68.27</v>
       </c>
       <c r="I31" t="n">
         <v>65.69757694059079</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.94</v>
+        <v>-10.88</v>
       </c>
       <c r="L31" t="n">
-        <v>6.11</v>
+        <v>11.37</v>
       </c>
       <c r="M31" t="n">
         <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>1.88</v>
+        <v>3.83</v>
       </c>
       <c r="O31" t="n">
         <v>-4.29</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45335.55208333334</v>
+        <v>45336.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>76.77</v>
+        <v>75.73</v>
       </c>
       <c r="I32" t="n">
         <v>76.19847779476632</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K32" t="n">
-        <v>12.45</v>
+        <v>10.93</v>
       </c>
       <c r="L32" t="n">
         <v>4.79</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>10.03</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45355.55208333334</v>
+        <v>45356.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>79.67</v>
+        <v>80.8</v>
       </c>
       <c r="I33" t="n">
         <v>79.92239873603981</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.2</v>
+        <v>-6.69</v>
       </c>
       <c r="L33" t="n">
-        <v>7.98</v>
+        <v>8.5</v>
       </c>
       <c r="M33" t="n">
         <v>1.95</v>
       </c>
       <c r="N33" t="n">
-        <v>2.83</v>
+        <v>5.85</v>
       </c>
       <c r="O33" t="n">
         <v>-0.65</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>6.06</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>77.3</v>
+        <v>74.3</v>
       </c>
       <c r="I34" t="n">
         <v>76.90762728775455</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.33</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>5.2</v>
+        <v>8.82</v>
       </c>
       <c r="M34" t="n">
         <v>2.13</v>
       </c>
       <c r="N34" t="n">
-        <v>4.62</v>
+        <v>5.05</v>
       </c>
       <c r="O34" t="n">
         <v>5.85</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45379.55208333334</v>
+        <v>45383.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>78.06999999999999</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="I35" t="n">
         <v>79.26610748615705</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.07</v>
+        <v>-7.09</v>
       </c>
       <c r="L35" t="n">
-        <v>6.19</v>
+        <v>7.44</v>
       </c>
       <c r="M35" t="n">
         <v>1.38</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.88</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>85.17</v>
+        <v>82.83</v>
       </c>
       <c r="I36" t="n">
         <v>82.95314551119638</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K36" t="n">
-        <v>7.04</v>
+        <v>4.1</v>
       </c>
       <c r="L36" t="n">
         <v>2.14</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>7.94</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45434.38541666666</v>
+        <v>45434.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>88.53</v>
+        <v>89.13</v>
       </c>
       <c r="I37" t="n">
         <v>88.60537330820591</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-6.88</v>
+        <v>-7.61</v>
       </c>
       <c r="L37" t="n">
         <v>9.050000000000001</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>5.82</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45491.55208333334</v>
+        <v>45492.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>136.93</v>
+        <v>129.32</v>
       </c>
       <c r="I38" t="n">
         <v>129.5816261806614</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>57</v>
+        <v>57.83333333333334</v>
       </c>
       <c r="K38" t="n">
-        <v>53.63</v>
+        <v>45.09</v>
       </c>
       <c r="L38" t="n">
         <v>2.02</v>
@@ -2607,7 +3062,7 @@
         <v>1.75</v>
       </c>
       <c r="N38" t="n">
-        <v>4.58</v>
+        <v>6.4</v>
       </c>
       <c r="O38" t="n">
         <v>1.55</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>9.49</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45524.55208333334</v>
+        <v>45525.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>126.4</v>
+        <v>128.43</v>
       </c>
       <c r="I39" t="n">
         <v>127.3437584195796</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K39" t="n">
-        <v>2.26</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L39" t="n">
         <v>6.09</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.16</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45540.55208333334</v>
+        <v>45541.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>128.81</v>
+        <v>125.87</v>
       </c>
       <c r="I40" t="n">
         <v>126.9134323431856</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K40" t="n">
-        <v>0.3</v>
+        <v>-1.99</v>
       </c>
       <c r="L40" t="n">
         <v>2.07</v>
@@ -2721,7 +3200,7 @@
         <v>1.07</v>
       </c>
       <c r="N40" t="n">
-        <v>1.38</v>
+        <v>2.9</v>
       </c>
       <c r="O40" t="n">
         <v>2.01</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>6.24</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45551.38541666666</v>
+        <v>45551.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>127.77</v>
+        <v>129.27</v>
       </c>
       <c r="I41" t="n">
         <v>129.2461454569151</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.51</v>
+        <v>-2.7</v>
       </c>
       <c r="L41" t="n">
-        <v>2.67</v>
+        <v>2.96</v>
       </c>
       <c r="M41" t="n">
         <v>0.7</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.19</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45568.55208333334</v>
+        <v>45569.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>135.97</v>
+        <v>134.35</v>
       </c>
       <c r="I42" t="n">
         <v>135.2430243072977</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>5.18</v>
+        <v>3.93</v>
       </c>
       <c r="L42" t="n">
         <v>2.22</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,25 +3386,25 @@
         <v>7.29</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45574.55208333334</v>
+        <v>45575.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>137.45</v>
+        <v>141.33</v>
       </c>
       <c r="I43" t="n">
         <v>140.8414348399738</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.31</v>
+        <v>-5.2</v>
       </c>
       <c r="L43" t="n">
-        <v>3.6</v>
+        <v>6.68</v>
       </c>
       <c r="M43" t="n">
-        <v>0.13</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N43" t="n">
         <v>3.29</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>7.11</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45583.55208333334</v>
+        <v>45586.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>136.53</v>
+        <v>133.19</v>
       </c>
       <c r="I44" t="n">
         <v>134.7260848496107</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.4</v>
+        <v>-5.76</v>
       </c>
       <c r="L44" t="n">
         <v>6.35</v>
@@ -2949,7 +3476,7 @@
         <v>0.75</v>
       </c>
       <c r="N44" t="n">
-        <v>2.18</v>
+        <v>2.71</v>
       </c>
       <c r="O44" t="n">
         <v>2.1</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>8.52</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45671.55208333334</v>
+        <v>45672.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>96.91</v>
+        <v>99.33</v>
       </c>
       <c r="I45" t="n">
         <v>99.13633910796631</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>85.16666666666667</v>
+        <v>86</v>
       </c>
       <c r="K45" t="n">
-        <v>27.24</v>
+        <v>25.42</v>
       </c>
       <c r="L45" t="n">
         <v>3.44</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>7.37</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45678.55208333334</v>
+        <v>45679.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>97.36</v>
+        <v>94.63</v>
       </c>
       <c r="I46" t="n">
         <v>94.90832535895369</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.98</v>
+        <v>-4.73</v>
       </c>
       <c r="L46" t="n">
-        <v>2.42</v>
+        <v>5.21</v>
       </c>
       <c r="M46" t="n">
         <v>0.59</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>7.9</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45722.38541666666</v>
+        <v>45722.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>84.5</v>
+        <v>84.97</v>
       </c>
       <c r="I47" t="n">
         <v>84.583702916584</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K47" t="n">
-        <v>10.7</v>
+        <v>10.21</v>
       </c>
       <c r="L47" t="n">
         <v>3.28</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45750.55208333334</v>
+        <v>45751.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>86.03</v>
+        <v>79.81</v>
       </c>
       <c r="I48" t="n">
         <v>84.67849896752068</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K48" t="n">
-        <v>1.25</v>
+        <v>-6.07</v>
       </c>
       <c r="L48" t="n">
         <v>6.3</v>
@@ -3177,7 +3752,7 @@
         <v>3.17</v>
       </c>
       <c r="N48" t="n">
-        <v>2.96</v>
+        <v>7.21</v>
       </c>
       <c r="O48" t="n">
         <v>3.08</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>13</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>78.79000000000001</v>
+        <v>84.27</v>
       </c>
       <c r="I49" t="n">
         <v>82.36102680246216</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>11</v>
       </c>
       <c r="K49" t="n">
-        <v>1.28</v>
+        <v>-5.59</v>
       </c>
       <c r="L49" t="n">
-        <v>7.38</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>6.34</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N49" t="n">
-        <v>4.4</v>
+        <v>8.1</v>
       </c>
       <c r="O49" t="n">
         <v>-7.21</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>10.42</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45824.38541666666</v>
+        <v>45824.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>102.27</v>
+        <v>101.89</v>
       </c>
       <c r="I50" t="n">
         <v>101.8926917889497</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>62</v>
+        <v>62.16666666666666</v>
       </c>
       <c r="K50" t="n">
-        <v>21.36</v>
+        <v>20.91</v>
       </c>
       <c r="L50" t="n">
         <v>1.12</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.65</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45840.55208333334</v>
+        <v>45841.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>101.83</v>
+        <v>103.58</v>
       </c>
       <c r="I51" t="n">
         <v>103.3526064447623</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>0.06</v>
+        <v>-1.66</v>
       </c>
       <c r="L51" t="n">
         <v>2.39</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>4.86</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45859.55208333334</v>
+        <v>45860.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>100.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I52" t="n">
         <v>99.59325770598137</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.68</v>
+        <v>-5.48</v>
       </c>
       <c r="L52" t="n">
-        <v>3.55</v>
+        <v>5.52</v>
       </c>
       <c r="M52" t="n">
         <v>0.2</v>
       </c>
       <c r="N52" t="n">
-        <v>2.03</v>
+        <v>3.27</v>
       </c>
       <c r="O52" t="n">
         <v>0.95</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>6.74</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45861.55208333334</v>
+        <v>45862.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>98.90000000000001</v>
+        <v>103.06</v>
       </c>
       <c r="I53" t="n">
         <v>102.3960761966841</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.02</v>
+        <v>-5.27</v>
       </c>
       <c r="L53" t="n">
-        <v>3.44</v>
+        <v>5.31</v>
       </c>
       <c r="M53" t="n">
         <v>0.21</v>
       </c>
       <c r="N53" t="n">
-        <v>1.44</v>
+        <v>4.43</v>
       </c>
       <c r="O53" t="n">
         <v>-3.27</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,25 +4145,25 @@
         <v>7.1</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45868.55208333334</v>
+        <v>45869.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>98.84999999999999</v>
+        <v>97.69</v>
       </c>
       <c r="I54" t="n">
         <v>98.11685290735556</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.08</v>
+        <v>-5.21</v>
       </c>
       <c r="L54" t="n">
-        <v>4.47</v>
+        <v>7.29</v>
       </c>
       <c r="M54" t="n">
-        <v>0.02</v>
+        <v>1.98</v>
       </c>
       <c r="N54" t="n">
         <v>3.61</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>5.1</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45887.55208333334</v>
+        <v>45888.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>94.09999999999999</v>
+        <v>98.67</v>
       </c>
       <c r="I55" t="n">
         <v>95.89265721954631</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K55" t="n">
-        <v>3.67</v>
+        <v>-1</v>
       </c>
       <c r="L55" t="n">
         <v>1.42</v>
@@ -3576,7 +4235,7 @@
         <v>1.02</v>
       </c>
       <c r="N55" t="n">
-        <v>3.04</v>
+        <v>5.84</v>
       </c>
       <c r="O55" t="n">
         <v>-1.7</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>9.23</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45895.55208333334</v>
+        <v>45897.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>93.08</v>
+        <v>92.38</v>
       </c>
       <c r="I56" t="n">
         <v>92.7280278561596</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>9</v>
       </c>
       <c r="K56" t="n">
-        <v>-5.67</v>
+        <v>-6.37</v>
       </c>
       <c r="L56" t="n">
-        <v>6.24</v>
+        <v>6.76</v>
       </c>
       <c r="M56" t="n">
         <v>0.33</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>5.66</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45905.55208333334</v>
+        <v>45908.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>94.56</v>
+        <v>98.59</v>
       </c>
       <c r="I57" t="n">
         <v>97.02672390572418</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.36</v>
+        <v>-6.72</v>
       </c>
       <c r="L57" t="n">
-        <v>6.52</v>
+        <v>7.05</v>
       </c>
       <c r="M57" t="n">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="N57" t="n">
-        <v>3.77</v>
+        <v>4.48</v>
       </c>
       <c r="O57" t="n">
         <v>-0.78</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.94</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45924.55208333334</v>
+        <v>45925.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>107.8</v>
+        <v>106.7</v>
       </c>
       <c r="I58" t="n">
         <v>107.2570530203622</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K58" t="n">
-        <v>9.34</v>
+        <v>8.23</v>
       </c>
       <c r="L58" t="n">
         <v>3.55</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.07</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45945.55208333334</v>
+        <v>45946.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>104.9</v>
+        <v>108.19</v>
       </c>
       <c r="I59" t="n">
         <v>106.7999776422362</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K59" t="n">
-        <v>1.69</v>
+        <v>-1.4</v>
       </c>
       <c r="L59" t="n">
         <v>1.87</v>
@@ -3804,7 +4511,7 @@
         <v>0.32</v>
       </c>
       <c r="N59" t="n">
-        <v>1.73</v>
+        <v>2.22</v>
       </c>
       <c r="O59" t="n">
         <v>-2.24</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>6.46</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45971.38541666666</v>
+        <v>45971.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>103.19</v>
+        <v>102.3</v>
       </c>
       <c r="I60" t="n">
         <v>102.441150940805</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>-4.62</v>
+        <v>-5.44</v>
       </c>
       <c r="L60" t="n">
         <v>5.65</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>5.12</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45974.38541666666</v>
+        <v>45974.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>105.79</v>
+        <v>111.61</v>
       </c>
       <c r="I61" t="n">
         <v>107.2960512120838</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.41</v>
+        <v>-9.1</v>
       </c>
       <c r="L61" t="n">
-        <v>4.77</v>
+        <v>9.24</v>
       </c>
       <c r="M61" t="n">
         <v>0.45</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46030.38541666666</v>
+        <v>46030.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>118.52</v>
+        <v>117.32</v>
       </c>
       <c r="I62" t="n">
         <v>118.2609232039156</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>55.83333333333334</v>
+        <v>56</v>
       </c>
       <c r="K62" t="n">
-        <v>6.19</v>
+        <v>5.12</v>
       </c>
       <c r="L62" t="n">
         <v>6.92</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>4.93</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>114.63</v>
+        <v>120.82</v>
       </c>
       <c r="I63" t="n">
         <v>115.211157216531</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>25</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>2.29</v>
+        <v>-2.98</v>
       </c>
       <c r="L63" t="n">
-        <v>1.36</v>
+        <v>6.96</v>
       </c>
       <c r="M63" t="n">
-        <v>1.6</v>
+        <v>8.17</v>
       </c>
       <c r="N63" t="n">
-        <v>3.66</v>
+        <v>5.91</v>
       </c>
       <c r="O63" t="n">
         <v>-1.66</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>7.73</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>133.1</v>
+        <v>127.05</v>
       </c>
       <c r="I64" t="n">
         <v>128.2779735185385</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K64" t="n">
-        <v>10.16</v>
+        <v>5.16</v>
       </c>
       <c r="L64" t="n">
         <v>3.95</v>
       </c>
       <c r="M64" t="n">
-        <v>1.45</v>
+        <v>5.18</v>
       </c>
       <c r="N64" t="n">
-        <v>2.79</v>
+        <v>3.34</v>
       </c>
       <c r="O64" t="n">
         <v>5.91</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>7.85</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>108.44</v>
+        <v>117.53</v>
       </c>
       <c r="I65" t="n">
         <v>114.122391564085</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K65" t="n">
-        <v>14.65</v>
+        <v>7.49</v>
       </c>
       <c r="L65" t="n">
         <v>3.74</v>
       </c>
       <c r="M65" t="n">
-        <v>3.84</v>
+        <v>5.91</v>
       </c>
       <c r="N65" t="n">
-        <v>4.46</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="O65" t="n">
         <v>-3.34</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>9.32</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46141.55208333334</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>123.45</v>
+        <v>120.22</v>
       </c>
       <c r="I66" t="n">
         <v>122.4135170382281</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K66" t="n">
-        <v>5.04</v>
+        <v>2.29</v>
       </c>
       <c r="L66" t="n">
         <v>3</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>7.84</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46148.55208333334</v>
+        <v>46149.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>127.65</v>
+        <v>130.46</v>
       </c>
       <c r="I67" t="n">
         <v>127.7048900178885</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K67" t="n">
-        <v>-6.18</v>
+        <v>-8.52</v>
       </c>
       <c r="L67" t="n">
-        <v>6.47</v>
+        <v>8.76</v>
       </c>
       <c r="M67" t="n">
         <v>0.7</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>7.97</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46210.38541666666</v>
+        <v>46210.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>143.88</v>
+        <v>143</v>
       </c>
       <c r="I68" t="n">
         <v>143.0878389842857</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>61</v>
+        <v>61.16666666666666</v>
       </c>
       <c r="K68" t="n">
-        <v>10.29</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="L68" t="n">
         <v>5.3</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>7.12</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46230.38541666666</v>
+        <v>46230.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>148.16</v>
+        <v>149.38</v>
       </c>
       <c r="I69" t="n">
         <v>149.2402818755083</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K69" t="n">
-        <v>-3.61</v>
+        <v>-4.46</v>
       </c>
       <c r="L69" t="n">
-        <v>4.18</v>
+        <v>4.55</v>
       </c>
       <c r="M69" t="n">
         <v>1.06</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>5.31</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46266.55208333334</v>
+        <v>46267.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>165</v>
+        <v>161.46</v>
       </c>
       <c r="I70" t="n">
         <v>163.6112312222869</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K70" t="n">
-        <v>10.46</v>
+        <v>8.09</v>
       </c>
       <c r="L70" t="n">
         <v>3.7</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>74</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7452,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.6</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7462,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7472,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>123.8</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7482,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7492,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7502,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48.1</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="11">
@@ -6653,7 +7512,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12">
@@ -6663,7 +7522,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -6673,7 +7532,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>76.8</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -6683,7 +7542,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.56</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7552,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.92</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7562,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.15</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7572,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>53.63</v>
+        <v>45.09</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7582,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.2</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7592,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.44</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7602,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.78</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="21">
@@ -6763,7 +7622,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -6773,7 +7632,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -6783,7 +7642,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="25">
@@ -6793,7 +7652,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.34</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -6803,7 +7662,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.38</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="27">
@@ -6813,7 +7672,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.03</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="28">
@@ -6823,7 +7682,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
